--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486934_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486934_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.885999999999999</v>
+        <v>9.288</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9099</v>
+        <v>5.2823</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9761</v>
+        <v>4.0058</v>
       </c>
       <c r="G2" t="n">
         <v>7.4913</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9492</v>
+        <v>1.3512</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6387</v>
+        <v>1.0111</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3105</v>
+        <v>0.3401</v>
       </c>
       <c r="V2" t="n">
         <v>0.2402</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>A. AKINWOLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0002</v>
+        <v>5.0136</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3996</v>
+        <v>4.0504</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6006</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.148</v>
+        <v>1.8039</v>
       </c>
       <c r="H3" t="n">
-        <v>1.661</v>
+        <v>0.4252</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5131</v>
+        <v>1.3786</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4316</v>
+        <v>2.9029</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8527</v>
+        <v>1.0614</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4211</v>
+        <v>1.8415</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2836</v>
+        <v>-1.099</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1917</v>
+        <v>-0.6362</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.092</v>
+        <v>-0.4629</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7988</v>
+        <v>1.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.968</v>
+        <v>0.9956</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1692</v>
+        <v>0.4544</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. AKINWOLE</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2344</v>
+        <v>4.5661</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0044</v>
+        <v>2.8766</v>
       </c>
       <c r="F4" t="n">
-        <v>1.23</v>
+        <v>1.6895</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8039</v>
+        <v>1.148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4252</v>
+        <v>1.661</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3786</v>
+        <v>-0.5131</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9029</v>
+        <v>1.4316</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0614</v>
+        <v>1.8527</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8415</v>
+        <v>-0.4211</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.099</v>
+        <v>-0.2836</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6362</v>
+        <v>-0.1917</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4629</v>
+        <v>-0.092</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8214</v>
+        <v>2.0534</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6708</v>
+        <v>1.3647</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0504</v>
+        <v>1.445</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7212</v>
+        <v>-0.0803</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9384</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0395</v>
+        <v>4.0878</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2617</v>
+        <v>3.2328</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7779</v>
+        <v>0.855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9717</v>
+        <v>1.5986</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5508</v>
+        <v>0.4702</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4208</v>
+        <v>1.1284</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4784</v>
+        <v>2.1558</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2683</v>
+        <v>1.0512</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2101</v>
+        <v>1.1047</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5067</v>
+        <v>-0.5572</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7174</v>
+        <v>-0.581</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2107</v>
+        <v>0.0238</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>1.4374</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1849</v>
+        <v>1.292</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8018999999999999</v>
+        <v>1.0769</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3831</v>
+        <v>0.2151</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.117</v>
+        <v>-0.2402</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.0006</v>
+        <v>3.6069</v>
       </c>
       <c r="E6" t="n">
-        <v>3.442</v>
+        <v>2.9522</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5586</v>
+        <v>0.6548</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5986</v>
+        <v>0.3845</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4702</v>
+        <v>0.7688</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1284</v>
+        <v>-0.3843</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1558</v>
+        <v>2.0728</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0512</v>
+        <v>1.5996</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1047</v>
+        <v>0.4732</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5572</v>
+        <v>-1.6883</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.581</v>
+        <v>-0.8308</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0238</v>
+        <v>-0.8575</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2048</v>
+        <v>2.1957</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2861</v>
+        <v>1.906</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0813</v>
+        <v>0.2897</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7865</v>
+        <v>3.3125</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1614</v>
+        <v>3.1571</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6251</v>
+        <v>0.1554</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3845</v>
+        <v>3.9717</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7688</v>
+        <v>1.5508</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3843</v>
+        <v>2.4208</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0728</v>
+        <v>4.4784</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5996</v>
+        <v>2.2683</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4732</v>
+        <v>2.2101</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6883</v>
+        <v>-0.5067</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8308</v>
+        <v>-0.7174</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8575</v>
+        <v>0.2107</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0267</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0534</v>
+        <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3753</v>
+        <v>1.4578</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1152</v>
+        <v>0.6973</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2601</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.117</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7936</v>
+        <v>3.193</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2161</v>
+        <v>2.1115</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5776</v>
+        <v>1.0815</v>
       </c>
       <c r="G8" t="n">
         <v>3.2485</v>
@@ -1078,13 +1078,13 @@
         <v>2.2588</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4405</v>
+        <v>0.8398</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9413</v>
+        <v>0.8367</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5009</v>
+        <v>0.003</v>
       </c>
       <c r="V8" t="n">
         <v>0.1314</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.6458</v>
+        <v>2.4977</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2946</v>
+        <v>0.7751</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3512</v>
+        <v>1.7226</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6083</v>
+        <v>0.5625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9765</v>
+        <v>-0.0421</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3682</v>
+        <v>0.6047</v>
       </c>
       <c r="J9" t="n">
-        <v>1.426</v>
+        <v>1.4378</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3076</v>
+        <v>0.6492</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1184</v>
+        <v>0.7886</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8177</v>
+        <v>-0.8753</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3311</v>
+        <v>-0.6913</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4866</v>
+        <v>-0.1839</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1068</v>
+        <v>-2.2588</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2588</v>
+        <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>3.0561</v>
+        <v>1.7299</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2547</v>
+        <v>1.5961</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8014</v>
+        <v>0.1338</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7207</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5597</v>
+        <v>1.8717</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2521</v>
+        <v>-0.1238</v>
       </c>
       <c r="F10" t="n">
+        <v>1.9955</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6083</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9765</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.3682</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="K10" t="n">
         <v>1.3076</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.0421</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.6047</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.4378</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.6492</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.7886</v>
+        <v>0.1184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8753</v>
+        <v>-0.8177</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6913</v>
+        <v>-0.3311</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1839</v>
+        <v>-0.4866</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2588</v>
+        <v>-4.1068</v>
       </c>
       <c r="R10" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7919</v>
+        <v>2.2819</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0731</v>
+        <v>1.8363</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2812</v>
+        <v>0.4457</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.8295</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3277</v>
+        <v>1.5352</v>
       </c>
       <c r="E11" t="n">
         <v>0.3447</v>
       </c>
       <c r="F11" t="n">
-        <v>0.983</v>
+        <v>1.1905</v>
       </c>
       <c r="G11" t="n">
         <v>1.4296</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.067</v>
+        <v>0.1405</v>
       </c>
       <c r="T11" t="n">
         <v>0.0736</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1406</v>
+        <v>0.0669</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4209</v>
+        <v>0.7521</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5215</v>
+        <v>0.1061</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9424</v>
+        <v>0.646</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1088</v>
@@ -1390,13 +1390,13 @@
         <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3798</v>
+        <v>0.711</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3216</v>
+        <v>0.306</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7014</v>
+        <v>0.405</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2875</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2837</v>
+        <v>0.2541</v>
       </c>
       <c r="E13" t="n">
         <v>-0.0265</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3102</v>
+        <v>0.2806</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6574</v>
@@ -1468,13 +1468,13 @@
         <v>0.616</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3251</v>
+        <v>0.2954</v>
       </c>
       <c r="T13" t="n">
         <v>0.0155</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3096</v>
+        <v>0.28</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>39.97860000000001</v>
+        <v>39.9787</v>
       </c>
       <c r="E14" t="n">
         <v>24.7385</v>
       </c>
       <c r="F14" t="n">
-        <v>15.2403</v>
+        <v>15.2404</v>
       </c>
       <c r="G14" t="n">
         <v>21.4807</v>
       </c>
       <c r="H14" t="n">
-        <v>9.180999999999999</v>
+        <v>9.180999999999997</v>
       </c>
       <c r="I14" t="n">
         <v>12.2996</v>
@@ -1537,7 +1537,7 @@
         <v>-1.3794</v>
       </c>
       <c r="P14" t="n">
-        <v>5.133399999999999</v>
+        <v>5.1334</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.4541</v>
@@ -1546,13 +1546,13 @@
         <v>22.5877</v>
       </c>
       <c r="S14" t="n">
-        <v>15.1102</v>
+        <v>15.1099</v>
       </c>
       <c r="T14" t="n">
         <v>11.7961</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3141</v>
+        <v>3.314</v>
       </c>
       <c r="V14" t="n">
         <v>-1.7454</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9987</v>
+        <v>3.2968</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5984</v>
+        <v>4.3892</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5998</v>
+        <v>-1.0924</v>
       </c>
       <c r="G15" t="n">
         <v>1.5701</v>
@@ -1624,13 +1624,13 @@
         <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1259</v>
+        <v>-1.8277</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4225</v>
+        <v>-0.6317</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.7034</v>
+        <v>-1.1961</v>
       </c>
       <c r="V15" t="n">
         <v>2.117</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.302</v>
+        <v>0.2594</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4948</v>
+        <v>-0.3902</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1928</v>
+        <v>0.6496</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2191</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.974</v>
+        <v>-0.4126</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3952</v>
+        <v>-0.2906</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5788</v>
+        <v>-0.122</v>
       </c>
       <c r="V16" t="n">
         <v>0.4805</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.8556</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="F17" t="n">
         <v>-0.7625999999999999</v>
@@ -1780,10 +1780,10 @@
         <v>0.4107</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3371</v>
+        <v>-0.2325</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1976</v>
+        <v>-0.093</v>
       </c>
       <c r="U17" t="n">
         <v>-0.1395</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9908</v>
+        <v>-1.1</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5117</v>
+        <v>-0.9373</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5025</v>
+        <v>-0.1627</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1109</v>
+        <v>0.3828</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8567</v>
+        <v>-0.1463</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.9676</v>
+        <v>0.5291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6397</v>
+        <v>0.7792</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5213</v>
+        <v>0.7397</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1184</v>
+        <v>0.0395</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.7506</v>
+        <v>-0.3963</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6646</v>
+        <v>-0.886</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.086</v>
+        <v>0.4897</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.4374</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>1.0267</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9147</v>
+        <v>-1.0722</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3093</v>
+        <v>-0.279</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3946</v>
+        <v>-0.7931</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5445</v>
+        <v>-1.1714</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2511</v>
+        <v>1.8939</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2935</v>
+        <v>-3.0653</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3828</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1463</v>
+        <v>-2.3616</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5291</v>
+        <v>1.6261</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7792</v>
+        <v>1.8312</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7397</v>
+        <v>-1.1153</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0395</v>
+        <v>2.9465</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3963</v>
+        <v>-2.5666</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.886</v>
+        <v>-1.2462</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4897</v>
+        <v>-1.3204</v>
       </c>
       <c r="P19" t="n">
+        <v>1.2321</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.4107</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.4374</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5167</v>
+        <v>-2.6064</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5928</v>
+        <v>-0.7053</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9238</v>
+        <v>-1.9012</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9089</v>
+        <v>-2.0596</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6847</v>
+        <v>1.5702</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.5935</v>
+        <v>-3.6298</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-2.1109</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3616</v>
+        <v>0.8567</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6261</v>
+        <v>-2.9676</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8312</v>
+        <v>2.6397</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1153</v>
+        <v>2.5213</v>
       </c>
       <c r="L20" t="n">
-        <v>2.9465</v>
+        <v>0.1184</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5666</v>
+        <v>-4.7506</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2462</v>
+        <v>-1.6646</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3204</v>
+        <v>-3.086</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4107</v>
+        <v>-1.4374</v>
       </c>
       <c r="R20" t="n">
         <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.3439</v>
+        <v>-0.154</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9145</v>
+        <v>0.3679</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.4294</v>
+        <v>-0.5219</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9384</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2717</v>
+        <v>-3.6832</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7876</v>
+        <v>-2.1014</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4841</v>
+        <v>-1.5818</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2783</v>
@@ -2092,13 +2092,13 @@
         <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1925</v>
+        <v>-1.604</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0195</v>
+        <v>-0.3333</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.173</v>
+        <v>-1.2707</v>
       </c>
       <c r="V21" t="n">
         <v>1.6366</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1036</v>
+        <v>-4.2633</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0067</v>
+        <v>-4.4837</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0969</v>
+        <v>0.2204</v>
       </c>
       <c r="G22" t="n">
         <v>-3.185</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.974</v>
+        <v>-0.1337</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3952</v>
+        <v>0.1278</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5788</v>
+        <v>-0.2615</v>
       </c>
       <c r="V22" t="n">
         <v>0.6982</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. GARCIA ROSELLO</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.333</v>
+        <v>-6.2556</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7554</v>
+        <v>-2.0794</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5776</v>
+        <v>-4.1763</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.662</v>
+        <v>-2.4167</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2492</v>
+        <v>-1.609</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4128</v>
+        <v>-0.8077</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0816</v>
+        <v>0.4081</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1947</v>
+        <v>0.474</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2763</v>
+        <v>-0.0659</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.5804</v>
+        <v>-2.8249</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4439</v>
+        <v>-2.083</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1365</v>
+        <v>-0.7418</v>
       </c>
       <c r="P23" t="n">
         <v>-0.8214</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0801</v>
+        <v>-2.2588</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2588</v>
+        <v>1.4374</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5622</v>
+        <v>-0.7691</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1045</v>
+        <v>-0.2287</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6667</v>
+        <v>-0.5404</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2875</v>
+        <v>-2.2484</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5893</v>
+        <v>-2.2484</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>M. GARCIA ROSELLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3638</v>
+        <v>-6.4324</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8702</v>
+        <v>-4.9646</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.4936</v>
+        <v>-1.4678</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4167</v>
+        <v>-3.662</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.609</v>
+        <v>-1.2492</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8077</v>
+        <v>-2.4128</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4081</v>
+        <v>-1.0816</v>
       </c>
       <c r="K24" t="n">
-        <v>0.474</v>
+        <v>0.1947</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0659</v>
+        <v>-1.2763</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8249</v>
+        <v>-2.5804</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.083</v>
+        <v>-1.4439</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7418</v>
+        <v>-1.1365</v>
       </c>
       <c r="P24" t="n">
         <v>-0.8214</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2588</v>
+        <v>-3.0801</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4374</v>
+        <v>2.2588</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8772</v>
+        <v>-0.6616</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0195</v>
+        <v>-0.1047</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8577</v>
+        <v>-0.5569</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.2484</v>
+        <v>-1.2875</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.2484</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4298</v>
+        <v>-6.7481</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1603</v>
+        <v>-3.8465</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2695</v>
+        <v>-2.9016</v>
       </c>
       <c r="G25" t="n">
         <v>-3.2083</v>
@@ -2404,13 +2404,13 @@
         <v>1.8481</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.552</v>
+        <v>-1.8703</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8486</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7034</v>
+        <v>-1.3355</v>
       </c>
       <c r="V25" t="n">
         <v>0.5893</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.769</v>
+        <v>-8.1762</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.5115</v>
+        <v>-4.1977</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.2575</v>
+        <v>-3.9786</v>
       </c>
       <c r="G26" t="n">
         <v>-4.5838</v>
@@ -2482,13 +2482,13 @@
         <v>1.6427</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5691</v>
+        <v>-0.9764</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9222</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6469</v>
+        <v>-0.368</v>
       </c>
       <c r="V26" t="n">
         <v>-1.1786</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-39.9786</v>
+        <v>-37.1892</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.2404</v>
+        <v>-15.2405</v>
       </c>
       <c r="F27" t="n">
-        <v>-24.7383</v>
+        <v>-21.9489</v>
       </c>
       <c r="G27" t="n">
         <v>-21.4804</v>
@@ -2533,7 +2533,7 @@
         <v>-12.2997</v>
       </c>
       <c r="J27" t="n">
-        <v>6.6223</v>
+        <v>6.622300000000001</v>
       </c>
       <c r="K27" t="n">
         <v>5.242800000000001</v>
@@ -2551,7 +2551,7 @@
         <v>-13.679</v>
       </c>
       <c r="P27" t="n">
-        <v>-5.1336</v>
+        <v>-5.133599999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-22.5876</v>
@@ -2560,13 +2560,13 @@
         <v>17.454</v>
       </c>
       <c r="S27" t="n">
-        <v>-15.1099</v>
+        <v>-12.3205</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.313800000000001</v>
+        <v>-3.3138</v>
       </c>
       <c r="U27" t="n">
-        <v>-11.796</v>
+        <v>-9.0068</v>
       </c>
       <c r="V27" t="n">
         <v>1.7455</v>
